--- a/00_output/02_market_characterization.xlsx
+++ b/00_output/02_market_characterization.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="customer_building_type_count" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment_count_per_building_type" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="equipment_count_per_building" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="efficiency_level_breakout" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,96 +449,6 @@
           <t>multifamily_li</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>large_restaurant</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>large_hospital</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>large_hotel</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>large_office</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>large_outpatient</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>large_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>large_retail</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>large_strip_mall</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>large_warehouse</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>small_restaurant</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>small_hospital</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>small_hotel</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>small_office</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>small_outpatient</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>small_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>small_retail</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>small_strip_mall</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>small_warehouse</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -567,60 +477,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>test_utility_1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
           <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>test_utility_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
         </is>
       </c>
     </row>
@@ -635,151 +497,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>competition_group_subgroup</t>
+          <t>competition_group</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>subgroup</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>single_family</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>multifamily</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>single_family_li</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>multifamily_li</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>large_restaurant</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>large_hospital</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>large_hotel</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>large_office</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>large_outpatient</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>large_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>large_retail</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>large_strip_mall</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>large_warehouse</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>small_restaurant</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>small_hospital</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>small_hotel</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>small_office</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>small_outpatient</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>small_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>small_retail</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>small_strip_mall</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>small_warehouse</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>heating_cooling_oil_furnace</t>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>oil_furnace</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>heating_cooling_gas_furnace</t>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>heating_cooling_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>refrigeration_full_size</t>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>full_size</t>
         </is>
       </c>
     </row>
@@ -794,235 +579,213 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>measure_name_competition_subgroup</t>
+          <t>competition_group</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>subgroup</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>single_family</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>multifamily</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>single_family_li</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>multifamily_li</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>large_restaurant</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>large_hospital</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>large_hotel</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>large_office</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>large_outpatient</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>large_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>large_retail</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>large_strip_mall</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>large_warehouse</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>small_restaurant</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>small_hospital</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>small_hotel</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>small_office</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>small_outpatient</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>small_primary_secondary_school</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>small_retail</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>small_strip_mall</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>small_warehouse</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>furnace_efficient_oil_residential_heating_cooling_oil_furnace</t>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>oil_furnace</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>furnace_efficient_oil_residential</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_baseline_oil_residential_heating_cooling_oil_furnace</t>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>oil_furnace</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>furnace_baseline_oil_residential</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_existing_oil_residential_heating_cooling_oil_furnace</t>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>oil_furnace</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>furnace_existing_oil_residential</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_efficient_natural_gas_residential_heating_cooling_gas_furnace</t>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>furnace_efficient_natural_gas_residential</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_baseline_natural_gas_residential_heating_cooling_gas_furnace</t>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>furnace_baseline_natural_gas_residential</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_existing_natural_gas_residential_heating_cooling_gas_furnace</t>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>furnace_existing_natural_gas_residential</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>central_ac_efficient_electric_residential_heating_cooling_cooling</t>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>fridge_efficient_electric_residential</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>central_ac_baseline_electric_residential_heating_cooling_cooling</t>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fridge_baseline_electric_residential</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>central_ac_existing_electric_residential_heating_cooling_cooling</t>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fridge_top10_electric_residential</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>room_ac_efficient_electric_residential_heating_cooling_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>room_ac_baseline_electric_residential_heating_cooling_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>room_ac_existing_electric_residential_heating_cooling_cooling</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>fridge_efficient_electric_residential_refrigeration_full_size</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>fridge_baseline_electric_residential_refrigeration_full_size</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>fridge_top10_electric_residential_refrigeration_full_size</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>fridge_existing_electric_residential_refrigeration_full_size</t>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fridge_existing_electric_residential</t>
         </is>
       </c>
     </row>

--- a/00_output/02_market_characterization.xlsx
+++ b/00_output/02_market_characterization.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>furnace_efficient_oil_residential</t>
+          <t>furnace_oil_efficient_residential</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>furnace_baseline_oil_residential</t>
+          <t>furnace_oil_baseline_residential</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>furnace_existing_oil_residential</t>
+          <t>furnace_oil_existing_residential</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>furnace_efficient_natural_gas_residential</t>
+          <t>furnace_natural_gas_efficient_residential</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>furnace_baseline_natural_gas_residential</t>
+          <t>furnace_natural_gas_baseline_residential</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>furnace_existing_natural_gas_residential</t>
+          <t>furnace_natural_gas_existing_residential</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fridge_efficient_electric_residential</t>
+          <t>fridge_electric_efficient_residential</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fridge_baseline_electric_residential</t>
+          <t>fridge_electric_baseline_residential</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fridge_top10_electric_residential</t>
+          <t>fridge_electric_top10_residential</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fridge_existing_electric_residential</t>
+          <t>fridge_electric_existing_residential</t>
         </is>
       </c>
     </row>

--- a/00_output/02_market_characterization.xlsx
+++ b/00_output/02_market_characterization.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fridge_electric_efficient_residential</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fridge_electric_baseline_residential</t>
+          <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fridge_electric_top10_residential</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fridge_electric_existing_residential</t>
+          <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
     </row>

--- a/00_output/02_market_characterization.xlsx
+++ b/00_output/02_market_characterization.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,20 +513,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>characterization_unit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>single_family</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>multifamily</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>single_family_li</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>multifamily_li</t>
         </is>
@@ -543,6 +548,11 @@
           <t>oil_furnace</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -555,6 +565,11 @@
           <t>gas_furnace</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>widget</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -565,6 +580,11 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>full_size</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>widget</t>
         </is>
       </c>
     </row>

--- a/00_output/02_market_characterization.xlsx
+++ b/00_output/02_market_characterization.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,7 +666,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gas_furnace</t>
+          <t>oil_furnace</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
     </row>
@@ -729,12 +729,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gas_furnace</t>
+          <t>oil_furnace</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
     </row>
@@ -746,78 +746,180 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gas_furnace</t>
+          <t>oil_furnace</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>refrigeration</t>
+          <t>heating_cooling</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>full_size</t>
+          <t>gas_furnace</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>refrigeration</t>
+          <t>heating_cooling</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>full_size</t>
+          <t>gas_furnace</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>refrigeration</t>
+          <t>heating_cooling</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>full_size</t>
+          <t>gas_furnace</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gas_furnace</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>refrigeration</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>full_size</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>full_size</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>

--- a/00_output/02_market_characterization.xlsx
+++ b/00_output/02_market_characterization.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,16 +27,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -44,12 +59,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,90 +460,118 @@
   </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>electric_utility</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>gas_utility</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>climate_zone</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>single_family</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>multifamily</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>single_family_li</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>multifamily_li</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>test_utility_1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>test_utility_1</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>test_utility_1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>test_utility_2</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>test_utility_1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1a</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -513,96 +584,118 @@
   </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>competition_group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>subgroup</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>characterization_unit</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>single_family</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>multifamily</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>single_family_li</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>multifamily_li</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>oil_furnace</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>widget</t>
         </is>
       </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>gas_furnace</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>widget</t>
         </is>
       </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>refrigeration</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>full_size</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>widget</t>
         </is>
       </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -615,317 +708,391 @@
   </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>competition_group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>subgroup</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>single_family</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>multifamily</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>single_family_li</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>multifamily_li</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>oil_furnace</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>furnace_oil_efficient_residential_1</t>
-        </is>
-      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential_1a</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>oil_furnace</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>furnace_oil_baseline_residential_1</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential_1a</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>oil_furnace</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>furnace_oil_existing_residential_1</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential_1a</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>oil_furnace</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>furnace_oil_efficient_residential_2</t>
-        </is>
-      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential_3b</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>oil_furnace</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>furnace_oil_baseline_residential_2</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential_3b</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>oil_furnace</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>furnace_oil_existing_residential_2</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential_3b</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>gas_furnace</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_efficient_residential_1</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_1a</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>gas_furnace</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_baseline_residential_1</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_1a</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>gas_furnace</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_existing_residential_1</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_1a</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>gas_furnace</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_efficient_residential_2</t>
-        </is>
-      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_3b</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>gas_furnace</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_baseline_residential_2</t>
-        </is>
-      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_3b</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>heating_cooling</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>gas_furnace</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_existing_residential_2</t>
-        </is>
-      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_3b</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>refrigeration</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>full_size</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>refrigeration</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>full_size</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>refrigeration</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>full_size</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>refrigeration</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>full_size</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/00_output/02_market_characterization.xlsx
+++ b/00_output/02_market_characterization.xlsx
@@ -462,7 +462,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -711,7 +711,7 @@
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
